--- a/Assets/Data/Excel/DialogueTable.xlsx
+++ b/Assets/Data/Excel/DialogueTable.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1030,6 +1030,195 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DLG_010_01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DLG_010</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>마을 근처에 슬라임이 나타나서 골치라네.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DLG_010_02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DLG_010</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한 마리만 처치해줄 수 있겠나?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DLG_010_03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DLG_010</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>플레이어</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Monologue</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>알겠습니다. 처치하고 올게요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DLG_011_01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DLG_011</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>아직 슬라임을 처치하지 못했나? 힘내게!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DLG_012_01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DLG_012</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>오, 해치웠군! 대단하네.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DLG_012_02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DLG_012</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>이 검을 가져가게. 내가 직접 만든 거라네.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DLG_012_03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DLG_012</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>플레이어</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Monologue</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>감사합니다!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
